--- a/data/qwen_gemma_benchmarks.xlsx
+++ b/data/qwen_gemma_benchmarks.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Qwen scores" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Gemma scores" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Third-party sources" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="OLL scores" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="LiveBench scores" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="ECI comparison" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="OLL cross-family" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Qwen scores" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gemma scores" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Third-party sources" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OLL scores" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LiveBench scores" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ECI comparison" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OLL cross-family" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Gemma scores'!$A$1:$K$394</definedName>
@@ -655,7 +655,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K650"/>
+  <dimension ref="A1:K704"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33117,6 +33117,2752 @@
       <c r="K650" t="inlineStr">
         <is>
           <t>huggingface.co/Qwen/Qwen3.5-0.8B card table, comparison columns (same evaluation run as the Qwen3.5 rows; extracted 2026-08)</t>
+        </is>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" t="inlineStr">
+        <is>
+          <t>Qwen</t>
+        </is>
+      </c>
+      <c r="B651" t="inlineStr">
+        <is>
+          <t>Qwen3.8</t>
+        </is>
+      </c>
+      <c r="C651" t="inlineStr">
+        <is>
+          <t>Qwen3.8-27B</t>
+        </is>
+      </c>
+      <c r="D651" t="n">
+        <v>27</v>
+      </c>
+      <c r="E651" t="inlineStr">
+        <is>
+          <t>Dense (multimodal)</t>
+        </is>
+      </c>
+      <c r="F651" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="G651" t="inlineStr">
+        <is>
+          <t>Thinking (default)</t>
+        </is>
+      </c>
+      <c r="H651" t="inlineStr">
+        <is>
+          <t>Terminal-Bench 2.1</t>
+        </is>
+      </c>
+      <c r="I651" t="inlineStr">
+        <is>
+          <t>Terminus scaffold</t>
+        </is>
+      </c>
+      <c r="J651" t="n">
+        <v>73</v>
+      </c>
+      <c r="K651" t="inlineStr">
+        <is>
+          <t>huggingface.co/Qwen/Qwen3.8-27B (live card, extracted 2026-08)</t>
+        </is>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" t="inlineStr">
+        <is>
+          <t>Qwen</t>
+        </is>
+      </c>
+      <c r="B652" t="inlineStr">
+        <is>
+          <t>Qwen3.6</t>
+        </is>
+      </c>
+      <c r="C652" t="inlineStr">
+        <is>
+          <t>Qwen3.6-27B</t>
+        </is>
+      </c>
+      <c r="D652" t="n">
+        <v>27</v>
+      </c>
+      <c r="E652" t="inlineStr">
+        <is>
+          <t>Dense (multimodal)</t>
+        </is>
+      </c>
+      <c r="F652" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="G652" t="inlineStr">
+        <is>
+          <t>Thinking (default)</t>
+        </is>
+      </c>
+      <c r="H652" t="inlineStr">
+        <is>
+          <t>Terminal-Bench 2.1</t>
+        </is>
+      </c>
+      <c r="I652" t="inlineStr">
+        <is>
+          <t>Terminus scaffold</t>
+        </is>
+      </c>
+      <c r="J652" t="n">
+        <v>63.4</v>
+      </c>
+      <c r="K652" t="inlineStr">
+        <is>
+          <t>huggingface.co/Qwen/Qwen3.8-27B card table, comparison column (Claude Code harness re-run; matches the Qwen3.6 card on all four overlapping benchmarks; extracted 2026-08)</t>
+        </is>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" t="inlineStr">
+        <is>
+          <t>Qwen</t>
+        </is>
+      </c>
+      <c r="B653" t="inlineStr">
+        <is>
+          <t>Qwen3.8</t>
+        </is>
+      </c>
+      <c r="C653" t="inlineStr">
+        <is>
+          <t>Qwen3.8-27B</t>
+        </is>
+      </c>
+      <c r="D653" t="n">
+        <v>27</v>
+      </c>
+      <c r="E653" t="inlineStr">
+        <is>
+          <t>Dense (multimodal)</t>
+        </is>
+      </c>
+      <c r="F653" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="G653" t="inlineStr">
+        <is>
+          <t>Thinking (default)</t>
+        </is>
+      </c>
+      <c r="H653" t="inlineStr">
+        <is>
+          <t>SWE-bench Pro</t>
+        </is>
+      </c>
+      <c r="I653" t="inlineStr">
+        <is>
+          <t>Claude Code harness</t>
+        </is>
+      </c>
+      <c r="J653" t="n">
+        <v>61.7</v>
+      </c>
+      <c r="K653" t="inlineStr">
+        <is>
+          <t>huggingface.co/Qwen/Qwen3.8-27B (live card, extracted 2026-08)</t>
+        </is>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" t="inlineStr">
+        <is>
+          <t>Qwen</t>
+        </is>
+      </c>
+      <c r="B654" t="inlineStr">
+        <is>
+          <t>Qwen3.8</t>
+        </is>
+      </c>
+      <c r="C654" t="inlineStr">
+        <is>
+          <t>Qwen3.8-27B</t>
+        </is>
+      </c>
+      <c r="D654" t="n">
+        <v>27</v>
+      </c>
+      <c r="E654" t="inlineStr">
+        <is>
+          <t>Dense (multimodal)</t>
+        </is>
+      </c>
+      <c r="F654" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="G654" t="inlineStr">
+        <is>
+          <t>Thinking (default)</t>
+        </is>
+      </c>
+      <c r="H654" t="inlineStr">
+        <is>
+          <t>NL2Repo-Bench</t>
+        </is>
+      </c>
+      <c r="I654" t="inlineStr"/>
+      <c r="J654" t="n">
+        <v>42.3</v>
+      </c>
+      <c r="K654" t="inlineStr">
+        <is>
+          <t>huggingface.co/Qwen/Qwen3.8-27B (live card, extracted 2026-08)</t>
+        </is>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" t="inlineStr">
+        <is>
+          <t>Qwen</t>
+        </is>
+      </c>
+      <c r="B655" t="inlineStr">
+        <is>
+          <t>Qwen3.6</t>
+        </is>
+      </c>
+      <c r="C655" t="inlineStr">
+        <is>
+          <t>Qwen3.6-27B</t>
+        </is>
+      </c>
+      <c r="D655" t="n">
+        <v>27</v>
+      </c>
+      <c r="E655" t="inlineStr">
+        <is>
+          <t>Dense (multimodal)</t>
+        </is>
+      </c>
+      <c r="F655" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="G655" t="inlineStr">
+        <is>
+          <t>Thinking (default)</t>
+        </is>
+      </c>
+      <c r="H655" t="inlineStr">
+        <is>
+          <t>NL2Repo-Bench</t>
+        </is>
+      </c>
+      <c r="I655" t="inlineStr"/>
+      <c r="J655" t="n">
+        <v>36.2</v>
+      </c>
+      <c r="K655" t="inlineStr">
+        <is>
+          <t>huggingface.co/Qwen/Qwen3.8-27B card table, comparison column (Claude Code harness re-run; matches the Qwen3.6 card on all four overlapping benchmarks; extracted 2026-08)</t>
+        </is>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" t="inlineStr">
+        <is>
+          <t>Qwen</t>
+        </is>
+      </c>
+      <c r="B656" t="inlineStr">
+        <is>
+          <t>Qwen3.8</t>
+        </is>
+      </c>
+      <c r="C656" t="inlineStr">
+        <is>
+          <t>Qwen3.8-27B</t>
+        </is>
+      </c>
+      <c r="D656" t="n">
+        <v>27</v>
+      </c>
+      <c r="E656" t="inlineStr">
+        <is>
+          <t>Dense (multimodal)</t>
+        </is>
+      </c>
+      <c r="F656" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="G656" t="inlineStr">
+        <is>
+          <t>Thinking (default)</t>
+        </is>
+      </c>
+      <c r="H656" t="inlineStr">
+        <is>
+          <t>DeepSWE 1.1</t>
+        </is>
+      </c>
+      <c r="I656" t="inlineStr">
+        <is>
+          <t>Claude Code harness</t>
+        </is>
+      </c>
+      <c r="J656" t="n">
+        <v>42.2</v>
+      </c>
+      <c r="K656" t="inlineStr">
+        <is>
+          <t>huggingface.co/Qwen/Qwen3.8-27B (live card, extracted 2026-08)</t>
+        </is>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" t="inlineStr">
+        <is>
+          <t>Qwen</t>
+        </is>
+      </c>
+      <c r="B657" t="inlineStr">
+        <is>
+          <t>Qwen3.6</t>
+        </is>
+      </c>
+      <c r="C657" t="inlineStr">
+        <is>
+          <t>Qwen3.6-27B</t>
+        </is>
+      </c>
+      <c r="D657" t="n">
+        <v>27</v>
+      </c>
+      <c r="E657" t="inlineStr">
+        <is>
+          <t>Dense (multimodal)</t>
+        </is>
+      </c>
+      <c r="F657" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="G657" t="inlineStr">
+        <is>
+          <t>Thinking (default)</t>
+        </is>
+      </c>
+      <c r="H657" t="inlineStr">
+        <is>
+          <t>DeepSWE 1.1</t>
+        </is>
+      </c>
+      <c r="I657" t="inlineStr">
+        <is>
+          <t>Claude Code harness</t>
+        </is>
+      </c>
+      <c r="J657" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="K657" t="inlineStr">
+        <is>
+          <t>huggingface.co/Qwen/Qwen3.8-27B card table, comparison column (Claude Code harness re-run; matches the Qwen3.6 card on all four overlapping benchmarks; extracted 2026-08)</t>
+        </is>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" t="inlineStr">
+        <is>
+          <t>Qwen</t>
+        </is>
+      </c>
+      <c r="B658" t="inlineStr">
+        <is>
+          <t>Qwen3.8</t>
+        </is>
+      </c>
+      <c r="C658" t="inlineStr">
+        <is>
+          <t>Qwen3.8-27B</t>
+        </is>
+      </c>
+      <c r="D658" t="n">
+        <v>27</v>
+      </c>
+      <c r="E658" t="inlineStr">
+        <is>
+          <t>Dense (multimodal)</t>
+        </is>
+      </c>
+      <c r="F658" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="G658" t="inlineStr">
+        <is>
+          <t>Thinking (default)</t>
+        </is>
+      </c>
+      <c r="H658" t="inlineStr">
+        <is>
+          <t>QwenSWEBench</t>
+        </is>
+      </c>
+      <c r="I658" t="inlineStr">
+        <is>
+          <t>Claude Code harness</t>
+        </is>
+      </c>
+      <c r="J658" t="n">
+        <v>79</v>
+      </c>
+      <c r="K658" t="inlineStr">
+        <is>
+          <t>huggingface.co/Qwen/Qwen3.8-27B (live card, extracted 2026-08)</t>
+        </is>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" t="inlineStr">
+        <is>
+          <t>Qwen</t>
+        </is>
+      </c>
+      <c r="B659" t="inlineStr">
+        <is>
+          <t>Qwen3.6</t>
+        </is>
+      </c>
+      <c r="C659" t="inlineStr">
+        <is>
+          <t>Qwen3.6-27B</t>
+        </is>
+      </c>
+      <c r="D659" t="n">
+        <v>27</v>
+      </c>
+      <c r="E659" t="inlineStr">
+        <is>
+          <t>Dense (multimodal)</t>
+        </is>
+      </c>
+      <c r="F659" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="G659" t="inlineStr">
+        <is>
+          <t>Thinking (default)</t>
+        </is>
+      </c>
+      <c r="H659" t="inlineStr">
+        <is>
+          <t>QwenSWEBench</t>
+        </is>
+      </c>
+      <c r="I659" t="inlineStr">
+        <is>
+          <t>Claude Code harness</t>
+        </is>
+      </c>
+      <c r="J659" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="K659" t="inlineStr">
+        <is>
+          <t>huggingface.co/Qwen/Qwen3.8-27B card table, comparison column (Claude Code harness re-run; matches the Qwen3.6 card on all four overlapping benchmarks; extracted 2026-08)</t>
+        </is>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" t="inlineStr">
+        <is>
+          <t>Qwen</t>
+        </is>
+      </c>
+      <c r="B660" t="inlineStr">
+        <is>
+          <t>Qwen3.8</t>
+        </is>
+      </c>
+      <c r="C660" t="inlineStr">
+        <is>
+          <t>Qwen3.8-27B</t>
+        </is>
+      </c>
+      <c r="D660" t="n">
+        <v>27</v>
+      </c>
+      <c r="E660" t="inlineStr">
+        <is>
+          <t>Dense (multimodal)</t>
+        </is>
+      </c>
+      <c r="F660" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="G660" t="inlineStr">
+        <is>
+          <t>Thinking (default)</t>
+        </is>
+      </c>
+      <c r="H660" t="inlineStr">
+        <is>
+          <t>CoWorkBench</t>
+        </is>
+      </c>
+      <c r="I660" t="inlineStr">
+        <is>
+          <t>avg@3, 8h timeout</t>
+        </is>
+      </c>
+      <c r="J660" t="n">
+        <v>70.7</v>
+      </c>
+      <c r="K660" t="inlineStr">
+        <is>
+          <t>huggingface.co/Qwen/Qwen3.8-27B (live card, extracted 2026-08)</t>
+        </is>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" t="inlineStr">
+        <is>
+          <t>Qwen</t>
+        </is>
+      </c>
+      <c r="B661" t="inlineStr">
+        <is>
+          <t>Qwen3.6</t>
+        </is>
+      </c>
+      <c r="C661" t="inlineStr">
+        <is>
+          <t>Qwen3.6-27B</t>
+        </is>
+      </c>
+      <c r="D661" t="n">
+        <v>27</v>
+      </c>
+      <c r="E661" t="inlineStr">
+        <is>
+          <t>Dense (multimodal)</t>
+        </is>
+      </c>
+      <c r="F661" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="G661" t="inlineStr">
+        <is>
+          <t>Thinking (default)</t>
+        </is>
+      </c>
+      <c r="H661" t="inlineStr">
+        <is>
+          <t>CoWorkBench</t>
+        </is>
+      </c>
+      <c r="I661" t="inlineStr">
+        <is>
+          <t>avg@3, 8h timeout</t>
+        </is>
+      </c>
+      <c r="J661" t="n">
+        <v>61</v>
+      </c>
+      <c r="K661" t="inlineStr">
+        <is>
+          <t>huggingface.co/Qwen/Qwen3.8-27B card table, comparison column (Claude Code harness re-run; matches the Qwen3.6 card on all four overlapping benchmarks; extracted 2026-08)</t>
+        </is>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" t="inlineStr">
+        <is>
+          <t>Qwen</t>
+        </is>
+      </c>
+      <c r="B662" t="inlineStr">
+        <is>
+          <t>Qwen3.8</t>
+        </is>
+      </c>
+      <c r="C662" t="inlineStr">
+        <is>
+          <t>Qwen3.8-27B</t>
+        </is>
+      </c>
+      <c r="D662" t="n">
+        <v>27</v>
+      </c>
+      <c r="E662" t="inlineStr">
+        <is>
+          <t>Dense (multimodal)</t>
+        </is>
+      </c>
+      <c r="F662" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="G662" t="inlineStr">
+        <is>
+          <t>Thinking (default)</t>
+        </is>
+      </c>
+      <c r="H662" t="inlineStr">
+        <is>
+          <t>JobBench</t>
+        </is>
+      </c>
+      <c r="I662" t="inlineStr"/>
+      <c r="J662" t="n">
+        <v>33.4</v>
+      </c>
+      <c r="K662" t="inlineStr">
+        <is>
+          <t>huggingface.co/Qwen/Qwen3.8-27B (live card, extracted 2026-08)</t>
+        </is>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" t="inlineStr">
+        <is>
+          <t>Qwen</t>
+        </is>
+      </c>
+      <c r="B663" t="inlineStr">
+        <is>
+          <t>Qwen3.6</t>
+        </is>
+      </c>
+      <c r="C663" t="inlineStr">
+        <is>
+          <t>Qwen3.6-27B</t>
+        </is>
+      </c>
+      <c r="D663" t="n">
+        <v>27</v>
+      </c>
+      <c r="E663" t="inlineStr">
+        <is>
+          <t>Dense (multimodal)</t>
+        </is>
+      </c>
+      <c r="F663" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="G663" t="inlineStr">
+        <is>
+          <t>Thinking (default)</t>
+        </is>
+      </c>
+      <c r="H663" t="inlineStr">
+        <is>
+          <t>JobBench</t>
+        </is>
+      </c>
+      <c r="I663" t="inlineStr"/>
+      <c r="J663" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="K663" t="inlineStr">
+        <is>
+          <t>huggingface.co/Qwen/Qwen3.8-27B card table, comparison column (Claude Code harness re-run; matches the Qwen3.6 card on all four overlapping benchmarks; extracted 2026-08)</t>
+        </is>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" t="inlineStr">
+        <is>
+          <t>Qwen</t>
+        </is>
+      </c>
+      <c r="B664" t="inlineStr">
+        <is>
+          <t>Qwen3.8</t>
+        </is>
+      </c>
+      <c r="C664" t="inlineStr">
+        <is>
+          <t>Qwen3.8-27B</t>
+        </is>
+      </c>
+      <c r="D664" t="n">
+        <v>27</v>
+      </c>
+      <c r="E664" t="inlineStr">
+        <is>
+          <t>Dense (multimodal)</t>
+        </is>
+      </c>
+      <c r="F664" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="G664" t="inlineStr">
+        <is>
+          <t>Thinking (default)</t>
+        </is>
+      </c>
+      <c r="H664" t="inlineStr">
+        <is>
+          <t>Agents' Last Exam (Pass@1)</t>
+        </is>
+      </c>
+      <c r="I664" t="inlineStr"/>
+      <c r="J664" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="K664" t="inlineStr">
+        <is>
+          <t>huggingface.co/Qwen/Qwen3.8-27B (live card, extracted 2026-08)</t>
+        </is>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" t="inlineStr">
+        <is>
+          <t>Qwen</t>
+        </is>
+      </c>
+      <c r="B665" t="inlineStr">
+        <is>
+          <t>Qwen3.6</t>
+        </is>
+      </c>
+      <c r="C665" t="inlineStr">
+        <is>
+          <t>Qwen3.6-27B</t>
+        </is>
+      </c>
+      <c r="D665" t="n">
+        <v>27</v>
+      </c>
+      <c r="E665" t="inlineStr">
+        <is>
+          <t>Dense (multimodal)</t>
+        </is>
+      </c>
+      <c r="F665" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="G665" t="inlineStr">
+        <is>
+          <t>Thinking (default)</t>
+        </is>
+      </c>
+      <c r="H665" t="inlineStr">
+        <is>
+          <t>Agents' Last Exam (Pass@1)</t>
+        </is>
+      </c>
+      <c r="I665" t="inlineStr"/>
+      <c r="J665" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="K665" t="inlineStr">
+        <is>
+          <t>huggingface.co/Qwen/Qwen3.8-27B card table, comparison column (Claude Code harness re-run; matches the Qwen3.6 card on all four overlapping benchmarks; extracted 2026-08)</t>
+        </is>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" t="inlineStr">
+        <is>
+          <t>Qwen</t>
+        </is>
+      </c>
+      <c r="B666" t="inlineStr">
+        <is>
+          <t>Qwen3.8</t>
+        </is>
+      </c>
+      <c r="C666" t="inlineStr">
+        <is>
+          <t>Qwen3.8-27B</t>
+        </is>
+      </c>
+      <c r="D666" t="n">
+        <v>27</v>
+      </c>
+      <c r="E666" t="inlineStr">
+        <is>
+          <t>Dense (multimodal)</t>
+        </is>
+      </c>
+      <c r="F666" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="G666" t="inlineStr">
+        <is>
+          <t>Thinking (default)</t>
+        </is>
+      </c>
+      <c r="H666" t="inlineStr">
+        <is>
+          <t>Agents' Last Exam (Score)</t>
+        </is>
+      </c>
+      <c r="I666" t="inlineStr"/>
+      <c r="J666" t="n">
+        <v>42.9</v>
+      </c>
+      <c r="K666" t="inlineStr">
+        <is>
+          <t>huggingface.co/Qwen/Qwen3.8-27B (live card, extracted 2026-08)</t>
+        </is>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" t="inlineStr">
+        <is>
+          <t>Qwen</t>
+        </is>
+      </c>
+      <c r="B667" t="inlineStr">
+        <is>
+          <t>Qwen3.6</t>
+        </is>
+      </c>
+      <c r="C667" t="inlineStr">
+        <is>
+          <t>Qwen3.6-27B</t>
+        </is>
+      </c>
+      <c r="D667" t="n">
+        <v>27</v>
+      </c>
+      <c r="E667" t="inlineStr">
+        <is>
+          <t>Dense (multimodal)</t>
+        </is>
+      </c>
+      <c r="F667" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="G667" t="inlineStr">
+        <is>
+          <t>Thinking (default)</t>
+        </is>
+      </c>
+      <c r="H667" t="inlineStr">
+        <is>
+          <t>Agents' Last Exam (Score)</t>
+        </is>
+      </c>
+      <c r="I667" t="inlineStr"/>
+      <c r="J667" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="K667" t="inlineStr">
+        <is>
+          <t>huggingface.co/Qwen/Qwen3.8-27B card table, comparison column (Claude Code harness re-run; matches the Qwen3.6 card on all four overlapping benchmarks; extracted 2026-08)</t>
+        </is>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" t="inlineStr">
+        <is>
+          <t>Qwen</t>
+        </is>
+      </c>
+      <c r="B668" t="inlineStr">
+        <is>
+          <t>Qwen3.8</t>
+        </is>
+      </c>
+      <c r="C668" t="inlineStr">
+        <is>
+          <t>Qwen3.8-27B</t>
+        </is>
+      </c>
+      <c r="D668" t="n">
+        <v>27</v>
+      </c>
+      <c r="E668" t="inlineStr">
+        <is>
+          <t>Dense (multimodal)</t>
+        </is>
+      </c>
+      <c r="F668" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="G668" t="inlineStr">
+        <is>
+          <t>Thinking (default)</t>
+        </is>
+      </c>
+      <c r="H668" t="inlineStr">
+        <is>
+          <t>IFBench</t>
+        </is>
+      </c>
+      <c r="I668" t="inlineStr"/>
+      <c r="J668" t="n">
+        <v>79.5</v>
+      </c>
+      <c r="K668" t="inlineStr">
+        <is>
+          <t>huggingface.co/Qwen/Qwen3.8-27B (live card, extracted 2026-08)</t>
+        </is>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" t="inlineStr">
+        <is>
+          <t>Qwen</t>
+        </is>
+      </c>
+      <c r="B669" t="inlineStr">
+        <is>
+          <t>Qwen3.6</t>
+        </is>
+      </c>
+      <c r="C669" t="inlineStr">
+        <is>
+          <t>Qwen3.6-27B</t>
+        </is>
+      </c>
+      <c r="D669" t="n">
+        <v>27</v>
+      </c>
+      <c r="E669" t="inlineStr">
+        <is>
+          <t>Dense (multimodal)</t>
+        </is>
+      </c>
+      <c r="F669" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="G669" t="inlineStr">
+        <is>
+          <t>Thinking (default)</t>
+        </is>
+      </c>
+      <c r="H669" t="inlineStr">
+        <is>
+          <t>IFBench</t>
+        </is>
+      </c>
+      <c r="I669" t="inlineStr"/>
+      <c r="J669" t="n">
+        <v>69.09999999999999</v>
+      </c>
+      <c r="K669" t="inlineStr">
+        <is>
+          <t>huggingface.co/Qwen/Qwen3.8-27B card table, comparison column (Claude Code harness re-run; matches the Qwen3.6 card on all four overlapping benchmarks; extracted 2026-08)</t>
+        </is>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" t="inlineStr">
+        <is>
+          <t>Qwen</t>
+        </is>
+      </c>
+      <c r="B670" t="inlineStr">
+        <is>
+          <t>Qwen3.8</t>
+        </is>
+      </c>
+      <c r="C670" t="inlineStr">
+        <is>
+          <t>Qwen3.8-27B</t>
+        </is>
+      </c>
+      <c r="D670" t="n">
+        <v>27</v>
+      </c>
+      <c r="E670" t="inlineStr">
+        <is>
+          <t>Dense (multimodal)</t>
+        </is>
+      </c>
+      <c r="F670" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="G670" t="inlineStr">
+        <is>
+          <t>Thinking (default)</t>
+        </is>
+      </c>
+      <c r="H670" t="inlineStr">
+        <is>
+          <t>GPQA-Diamond</t>
+        </is>
+      </c>
+      <c r="I670" t="inlineStr"/>
+      <c r="J670" t="n">
+        <v>89.2</v>
+      </c>
+      <c r="K670" t="inlineStr">
+        <is>
+          <t>huggingface.co/Qwen/Qwen3.8-27B (live card, extracted 2026-08)</t>
+        </is>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" t="inlineStr">
+        <is>
+          <t>Qwen</t>
+        </is>
+      </c>
+      <c r="B671" t="inlineStr">
+        <is>
+          <t>Qwen3.8</t>
+        </is>
+      </c>
+      <c r="C671" t="inlineStr">
+        <is>
+          <t>Qwen3.8-27B</t>
+        </is>
+      </c>
+      <c r="D671" t="n">
+        <v>27</v>
+      </c>
+      <c r="E671" t="inlineStr">
+        <is>
+          <t>Dense (multimodal)</t>
+        </is>
+      </c>
+      <c r="F671" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="G671" t="inlineStr">
+        <is>
+          <t>Thinking (default)</t>
+        </is>
+      </c>
+      <c r="H671" t="inlineStr">
+        <is>
+          <t>HLE</t>
+        </is>
+      </c>
+      <c r="I671" t="inlineStr">
+        <is>
+          <t>no tools</t>
+        </is>
+      </c>
+      <c r="J671" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="K671" t="inlineStr">
+        <is>
+          <t>huggingface.co/Qwen/Qwen3.8-27B (live card, extracted 2026-08)</t>
+        </is>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" t="inlineStr">
+        <is>
+          <t>Qwen</t>
+        </is>
+      </c>
+      <c r="B672" t="inlineStr">
+        <is>
+          <t>Qwen3.8</t>
+        </is>
+      </c>
+      <c r="C672" t="inlineStr">
+        <is>
+          <t>Qwen3.8-27B</t>
+        </is>
+      </c>
+      <c r="D672" t="n">
+        <v>27</v>
+      </c>
+      <c r="E672" t="inlineStr">
+        <is>
+          <t>Dense (multimodal)</t>
+        </is>
+      </c>
+      <c r="F672" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="G672" t="inlineStr">
+        <is>
+          <t>Thinking (default)</t>
+        </is>
+      </c>
+      <c r="H672" t="inlineStr">
+        <is>
+          <t>LiveCodeBench</t>
+        </is>
+      </c>
+      <c r="I672" t="inlineStr">
+        <is>
+          <t>v6</t>
+        </is>
+      </c>
+      <c r="J672" t="n">
+        <v>90.3</v>
+      </c>
+      <c r="K672" t="inlineStr">
+        <is>
+          <t>huggingface.co/Qwen/Qwen3.8-27B (live card, extracted 2026-08)</t>
+        </is>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" t="inlineStr">
+        <is>
+          <t>Qwen</t>
+        </is>
+      </c>
+      <c r="B673" t="inlineStr">
+        <is>
+          <t>Qwen3.8</t>
+        </is>
+      </c>
+      <c r="C673" t="inlineStr">
+        <is>
+          <t>Qwen3.8-27B</t>
+        </is>
+      </c>
+      <c r="D673" t="n">
+        <v>27</v>
+      </c>
+      <c r="E673" t="inlineStr">
+        <is>
+          <t>Dense (multimodal)</t>
+        </is>
+      </c>
+      <c r="F673" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="G673" t="inlineStr">
+        <is>
+          <t>Thinking (default)</t>
+        </is>
+      </c>
+      <c r="H673" t="inlineStr">
+        <is>
+          <t>OSWorld-Verified</t>
+        </is>
+      </c>
+      <c r="I673" t="inlineStr"/>
+      <c r="J673" t="n">
+        <v>84.3</v>
+      </c>
+      <c r="K673" t="inlineStr">
+        <is>
+          <t>huggingface.co/Qwen/Qwen3.8-27B (live card, extracted 2026-08)</t>
+        </is>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" t="inlineStr">
+        <is>
+          <t>Qwen</t>
+        </is>
+      </c>
+      <c r="B674" t="inlineStr">
+        <is>
+          <t>Qwen3.6</t>
+        </is>
+      </c>
+      <c r="C674" t="inlineStr">
+        <is>
+          <t>Qwen3.6-27B</t>
+        </is>
+      </c>
+      <c r="D674" t="n">
+        <v>27</v>
+      </c>
+      <c r="E674" t="inlineStr">
+        <is>
+          <t>Dense (multimodal)</t>
+        </is>
+      </c>
+      <c r="F674" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="G674" t="inlineStr">
+        <is>
+          <t>Thinking (default)</t>
+        </is>
+      </c>
+      <c r="H674" t="inlineStr">
+        <is>
+          <t>OSWorld-Verified</t>
+        </is>
+      </c>
+      <c r="I674" t="inlineStr"/>
+      <c r="J674" t="n">
+        <v>63.9</v>
+      </c>
+      <c r="K674" t="inlineStr">
+        <is>
+          <t>huggingface.co/Qwen/Qwen3.8-27B card table, comparison column (Claude Code harness re-run; matches the Qwen3.6 card on all four overlapping benchmarks; extracted 2026-08)</t>
+        </is>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" t="inlineStr">
+        <is>
+          <t>Qwen</t>
+        </is>
+      </c>
+      <c r="B675" t="inlineStr">
+        <is>
+          <t>Qwen3.8</t>
+        </is>
+      </c>
+      <c r="C675" t="inlineStr">
+        <is>
+          <t>Qwen3.8-27B</t>
+        </is>
+      </c>
+      <c r="D675" t="n">
+        <v>27</v>
+      </c>
+      <c r="E675" t="inlineStr">
+        <is>
+          <t>Dense (multimodal)</t>
+        </is>
+      </c>
+      <c r="F675" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="G675" t="inlineStr">
+        <is>
+          <t>Thinking (default)</t>
+        </is>
+      </c>
+      <c r="H675" t="inlineStr">
+        <is>
+          <t>WebArena-Verified</t>
+        </is>
+      </c>
+      <c r="I675" t="inlineStr"/>
+      <c r="J675" t="n">
+        <v>64.8</v>
+      </c>
+      <c r="K675" t="inlineStr">
+        <is>
+          <t>huggingface.co/Qwen/Qwen3.8-27B (live card, extracted 2026-08)</t>
+        </is>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" t="inlineStr">
+        <is>
+          <t>Qwen</t>
+        </is>
+      </c>
+      <c r="B676" t="inlineStr">
+        <is>
+          <t>Qwen3.6</t>
+        </is>
+      </c>
+      <c r="C676" t="inlineStr">
+        <is>
+          <t>Qwen3.6-27B</t>
+        </is>
+      </c>
+      <c r="D676" t="n">
+        <v>27</v>
+      </c>
+      <c r="E676" t="inlineStr">
+        <is>
+          <t>Dense (multimodal)</t>
+        </is>
+      </c>
+      <c r="F676" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="G676" t="inlineStr">
+        <is>
+          <t>Thinking (default)</t>
+        </is>
+      </c>
+      <c r="H676" t="inlineStr">
+        <is>
+          <t>WebArena-Verified</t>
+        </is>
+      </c>
+      <c r="I676" t="inlineStr"/>
+      <c r="J676" t="n">
+        <v>48.8</v>
+      </c>
+      <c r="K676" t="inlineStr">
+        <is>
+          <t>huggingface.co/Qwen/Qwen3.8-27B card table, comparison column (Claude Code harness re-run; matches the Qwen3.6 card on all four overlapping benchmarks; extracted 2026-08)</t>
+        </is>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" t="inlineStr">
+        <is>
+          <t>Qwen</t>
+        </is>
+      </c>
+      <c r="B677" t="inlineStr">
+        <is>
+          <t>Qwen3.8</t>
+        </is>
+      </c>
+      <c r="C677" t="inlineStr">
+        <is>
+          <t>Qwen3.8-27B</t>
+        </is>
+      </c>
+      <c r="D677" t="n">
+        <v>27</v>
+      </c>
+      <c r="E677" t="inlineStr">
+        <is>
+          <t>Dense (multimodal)</t>
+        </is>
+      </c>
+      <c r="F677" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="G677" t="inlineStr">
+        <is>
+          <t>Thinking (default)</t>
+        </is>
+      </c>
+      <c r="H677" t="inlineStr">
+        <is>
+          <t>AndroidWorld</t>
+        </is>
+      </c>
+      <c r="I677" t="inlineStr"/>
+      <c r="J677" t="n">
+        <v>81.90000000000001</v>
+      </c>
+      <c r="K677" t="inlineStr">
+        <is>
+          <t>huggingface.co/Qwen/Qwen3.8-27B (live card, extracted 2026-08)</t>
+        </is>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" t="inlineStr">
+        <is>
+          <t>Qwen</t>
+        </is>
+      </c>
+      <c r="B678" t="inlineStr">
+        <is>
+          <t>Qwen3.6</t>
+        </is>
+      </c>
+      <c r="C678" t="inlineStr">
+        <is>
+          <t>Qwen3.6-27B</t>
+        </is>
+      </c>
+      <c r="D678" t="n">
+        <v>27</v>
+      </c>
+      <c r="E678" t="inlineStr">
+        <is>
+          <t>Dense (multimodal)</t>
+        </is>
+      </c>
+      <c r="F678" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="G678" t="inlineStr">
+        <is>
+          <t>Thinking (default)</t>
+        </is>
+      </c>
+      <c r="H678" t="inlineStr">
+        <is>
+          <t>AndroidWorld</t>
+        </is>
+      </c>
+      <c r="I678" t="inlineStr"/>
+      <c r="J678" t="n">
+        <v>70.3</v>
+      </c>
+      <c r="K678" t="inlineStr">
+        <is>
+          <t>huggingface.co/Qwen/Qwen3.8-27B card table, comparison column (Claude Code harness re-run; matches the Qwen3.6 card on all four overlapping benchmarks; extracted 2026-08)</t>
+        </is>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" t="inlineStr">
+        <is>
+          <t>Qwen</t>
+        </is>
+      </c>
+      <c r="B679" t="inlineStr">
+        <is>
+          <t>Qwen3.8</t>
+        </is>
+      </c>
+      <c r="C679" t="inlineStr">
+        <is>
+          <t>Qwen3.8-27B</t>
+        </is>
+      </c>
+      <c r="D679" t="n">
+        <v>27</v>
+      </c>
+      <c r="E679" t="inlineStr">
+        <is>
+          <t>Dense (multimodal)</t>
+        </is>
+      </c>
+      <c r="F679" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="G679" t="inlineStr">
+        <is>
+          <t>Thinking (default)</t>
+        </is>
+      </c>
+      <c r="H679" t="inlineStr">
+        <is>
+          <t>RecreationBench</t>
+        </is>
+      </c>
+      <c r="I679" t="inlineStr"/>
+      <c r="J679" t="n">
+        <v>47.1</v>
+      </c>
+      <c r="K679" t="inlineStr">
+        <is>
+          <t>huggingface.co/Qwen/Qwen3.8-27B (live card, extracted 2026-08)</t>
+        </is>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" t="inlineStr">
+        <is>
+          <t>Qwen</t>
+        </is>
+      </c>
+      <c r="B680" t="inlineStr">
+        <is>
+          <t>Qwen3.6</t>
+        </is>
+      </c>
+      <c r="C680" t="inlineStr">
+        <is>
+          <t>Qwen3.6-27B</t>
+        </is>
+      </c>
+      <c r="D680" t="n">
+        <v>27</v>
+      </c>
+      <c r="E680" t="inlineStr">
+        <is>
+          <t>Dense (multimodal)</t>
+        </is>
+      </c>
+      <c r="F680" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="G680" t="inlineStr">
+        <is>
+          <t>Thinking (default)</t>
+        </is>
+      </c>
+      <c r="H680" t="inlineStr">
+        <is>
+          <t>RecreationBench</t>
+        </is>
+      </c>
+      <c r="I680" t="inlineStr"/>
+      <c r="J680" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="K680" t="inlineStr">
+        <is>
+          <t>huggingface.co/Qwen/Qwen3.8-27B card table, comparison column (Claude Code harness re-run; matches the Qwen3.6 card on all four overlapping benchmarks; extracted 2026-08)</t>
+        </is>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" t="inlineStr">
+        <is>
+          <t>Qwen</t>
+        </is>
+      </c>
+      <c r="B681" t="inlineStr">
+        <is>
+          <t>Qwen3.8</t>
+        </is>
+      </c>
+      <c r="C681" t="inlineStr">
+        <is>
+          <t>Qwen3.8-27B</t>
+        </is>
+      </c>
+      <c r="D681" t="n">
+        <v>27</v>
+      </c>
+      <c r="E681" t="inlineStr">
+        <is>
+          <t>Dense (multimodal)</t>
+        </is>
+      </c>
+      <c r="F681" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="G681" t="inlineStr">
+        <is>
+          <t>Thinking (default)</t>
+        </is>
+      </c>
+      <c r="H681" t="inlineStr">
+        <is>
+          <t>ClawEval-MM (Pass@3)</t>
+        </is>
+      </c>
+      <c r="I681" t="inlineStr"/>
+      <c r="J681" t="n">
+        <v>57.4</v>
+      </c>
+      <c r="K681" t="inlineStr">
+        <is>
+          <t>huggingface.co/Qwen/Qwen3.8-27B (live card, extracted 2026-08)</t>
+        </is>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" t="inlineStr">
+        <is>
+          <t>Qwen</t>
+        </is>
+      </c>
+      <c r="B682" t="inlineStr">
+        <is>
+          <t>Qwen3.6</t>
+        </is>
+      </c>
+      <c r="C682" t="inlineStr">
+        <is>
+          <t>Qwen3.6-27B</t>
+        </is>
+      </c>
+      <c r="D682" t="n">
+        <v>27</v>
+      </c>
+      <c r="E682" t="inlineStr">
+        <is>
+          <t>Dense (multimodal)</t>
+        </is>
+      </c>
+      <c r="F682" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="G682" t="inlineStr">
+        <is>
+          <t>Thinking (default)</t>
+        </is>
+      </c>
+      <c r="H682" t="inlineStr">
+        <is>
+          <t>ClawEval-MM (Pass@3)</t>
+        </is>
+      </c>
+      <c r="I682" t="inlineStr"/>
+      <c r="J682" t="n">
+        <v>56.9</v>
+      </c>
+      <c r="K682" t="inlineStr">
+        <is>
+          <t>huggingface.co/Qwen/Qwen3.8-27B card table, comparison column (Claude Code harness re-run; matches the Qwen3.6 card on all four overlapping benchmarks; extracted 2026-08)</t>
+        </is>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" t="inlineStr">
+        <is>
+          <t>Qwen</t>
+        </is>
+      </c>
+      <c r="B683" t="inlineStr">
+        <is>
+          <t>Qwen3.8</t>
+        </is>
+      </c>
+      <c r="C683" t="inlineStr">
+        <is>
+          <t>Qwen3.8-27B</t>
+        </is>
+      </c>
+      <c r="D683" t="n">
+        <v>27</v>
+      </c>
+      <c r="E683" t="inlineStr">
+        <is>
+          <t>Dense (multimodal)</t>
+        </is>
+      </c>
+      <c r="F683" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="G683" t="inlineStr">
+        <is>
+          <t>Thinking (default)</t>
+        </is>
+      </c>
+      <c r="H683" t="inlineStr">
+        <is>
+          <t>ClawEval-MM (Average)</t>
+        </is>
+      </c>
+      <c r="I683" t="inlineStr"/>
+      <c r="J683" t="n">
+        <v>50.4</v>
+      </c>
+      <c r="K683" t="inlineStr">
+        <is>
+          <t>huggingface.co/Qwen/Qwen3.8-27B (live card, extracted 2026-08)</t>
+        </is>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" t="inlineStr">
+        <is>
+          <t>Qwen</t>
+        </is>
+      </c>
+      <c r="B684" t="inlineStr">
+        <is>
+          <t>Qwen3.6</t>
+        </is>
+      </c>
+      <c r="C684" t="inlineStr">
+        <is>
+          <t>Qwen3.6-27B</t>
+        </is>
+      </c>
+      <c r="D684" t="n">
+        <v>27</v>
+      </c>
+      <c r="E684" t="inlineStr">
+        <is>
+          <t>Dense (multimodal)</t>
+        </is>
+      </c>
+      <c r="F684" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="G684" t="inlineStr">
+        <is>
+          <t>Thinking (default)</t>
+        </is>
+      </c>
+      <c r="H684" t="inlineStr">
+        <is>
+          <t>ClawEval-MM (Average)</t>
+        </is>
+      </c>
+      <c r="I684" t="inlineStr"/>
+      <c r="J684" t="n">
+        <v>42.6</v>
+      </c>
+      <c r="K684" t="inlineStr">
+        <is>
+          <t>huggingface.co/Qwen/Qwen3.8-27B card table, comparison column (Claude Code harness re-run; matches the Qwen3.6 card on all four overlapping benchmarks; extracted 2026-08)</t>
+        </is>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" t="inlineStr">
+        <is>
+          <t>Qwen</t>
+        </is>
+      </c>
+      <c r="B685" t="inlineStr">
+        <is>
+          <t>Qwen3.8</t>
+        </is>
+      </c>
+      <c r="C685" t="inlineStr">
+        <is>
+          <t>Qwen3.8-27B</t>
+        </is>
+      </c>
+      <c r="D685" t="n">
+        <v>27</v>
+      </c>
+      <c r="E685" t="inlineStr">
+        <is>
+          <t>Dense (multimodal)</t>
+        </is>
+      </c>
+      <c r="F685" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="G685" t="inlineStr">
+        <is>
+          <t>Thinking (default)</t>
+        </is>
+      </c>
+      <c r="H685" t="inlineStr">
+        <is>
+          <t>SWE-MM</t>
+        </is>
+      </c>
+      <c r="I685" t="inlineStr"/>
+      <c r="J685" t="n">
+        <v>38.6</v>
+      </c>
+      <c r="K685" t="inlineStr">
+        <is>
+          <t>huggingface.co/Qwen/Qwen3.8-27B (live card, extracted 2026-08)</t>
+        </is>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" t="inlineStr">
+        <is>
+          <t>Qwen</t>
+        </is>
+      </c>
+      <c r="B686" t="inlineStr">
+        <is>
+          <t>Qwen3.6</t>
+        </is>
+      </c>
+      <c r="C686" t="inlineStr">
+        <is>
+          <t>Qwen3.6-27B</t>
+        </is>
+      </c>
+      <c r="D686" t="n">
+        <v>27</v>
+      </c>
+      <c r="E686" t="inlineStr">
+        <is>
+          <t>Dense (multimodal)</t>
+        </is>
+      </c>
+      <c r="F686" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="G686" t="inlineStr">
+        <is>
+          <t>Thinking (default)</t>
+        </is>
+      </c>
+      <c r="H686" t="inlineStr">
+        <is>
+          <t>SWE-MM</t>
+        </is>
+      </c>
+      <c r="I686" t="inlineStr"/>
+      <c r="J686" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="K686" t="inlineStr">
+        <is>
+          <t>huggingface.co/Qwen/Qwen3.8-27B card table, comparison column (Claude Code harness re-run; matches the Qwen3.6 card on all four overlapping benchmarks; extracted 2026-08)</t>
+        </is>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" t="inlineStr">
+        <is>
+          <t>Qwen</t>
+        </is>
+      </c>
+      <c r="B687" t="inlineStr">
+        <is>
+          <t>Qwen3.8</t>
+        </is>
+      </c>
+      <c r="C687" t="inlineStr">
+        <is>
+          <t>Qwen3.8-27B</t>
+        </is>
+      </c>
+      <c r="D687" t="n">
+        <v>27</v>
+      </c>
+      <c r="E687" t="inlineStr">
+        <is>
+          <t>Dense (multimodal)</t>
+        </is>
+      </c>
+      <c r="F687" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="G687" t="inlineStr">
+        <is>
+          <t>Thinking (default)</t>
+        </is>
+      </c>
+      <c r="H687" t="inlineStr">
+        <is>
+          <t>Vision2Web</t>
+        </is>
+      </c>
+      <c r="I687" t="inlineStr"/>
+      <c r="J687" t="n">
+        <v>62.9</v>
+      </c>
+      <c r="K687" t="inlineStr">
+        <is>
+          <t>huggingface.co/Qwen/Qwen3.8-27B (live card, extracted 2026-08)</t>
+        </is>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" t="inlineStr">
+        <is>
+          <t>Qwen</t>
+        </is>
+      </c>
+      <c r="B688" t="inlineStr">
+        <is>
+          <t>Qwen3.6</t>
+        </is>
+      </c>
+      <c r="C688" t="inlineStr">
+        <is>
+          <t>Qwen3.6-27B</t>
+        </is>
+      </c>
+      <c r="D688" t="n">
+        <v>27</v>
+      </c>
+      <c r="E688" t="inlineStr">
+        <is>
+          <t>Dense (multimodal)</t>
+        </is>
+      </c>
+      <c r="F688" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="G688" t="inlineStr">
+        <is>
+          <t>Thinking (default)</t>
+        </is>
+      </c>
+      <c r="H688" t="inlineStr">
+        <is>
+          <t>Vision2Web</t>
+        </is>
+      </c>
+      <c r="I688" t="inlineStr"/>
+      <c r="J688" t="n">
+        <v>45</v>
+      </c>
+      <c r="K688" t="inlineStr">
+        <is>
+          <t>huggingface.co/Qwen/Qwen3.8-27B card table, comparison column (Claude Code harness re-run; matches the Qwen3.6 card on all four overlapping benchmarks; extracted 2026-08)</t>
+        </is>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" t="inlineStr">
+        <is>
+          <t>Qwen</t>
+        </is>
+      </c>
+      <c r="B689" t="inlineStr">
+        <is>
+          <t>Qwen3.8</t>
+        </is>
+      </c>
+      <c r="C689" t="inlineStr">
+        <is>
+          <t>Qwen3.8-27B</t>
+        </is>
+      </c>
+      <c r="D689" t="n">
+        <v>27</v>
+      </c>
+      <c r="E689" t="inlineStr">
+        <is>
+          <t>Dense (multimodal)</t>
+        </is>
+      </c>
+      <c r="F689" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="G689" t="inlineStr">
+        <is>
+          <t>Thinking (default)</t>
+        </is>
+      </c>
+      <c r="H689" t="inlineStr">
+        <is>
+          <t>MathVision (no CI)</t>
+        </is>
+      </c>
+      <c r="I689" t="inlineStr">
+        <is>
+          <t>vision</t>
+        </is>
+      </c>
+      <c r="J689" t="n">
+        <v>90</v>
+      </c>
+      <c r="K689" t="inlineStr">
+        <is>
+          <t>huggingface.co/Qwen/Qwen3.8-27B (live card, extracted 2026-08)</t>
+        </is>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" t="inlineStr">
+        <is>
+          <t>Qwen</t>
+        </is>
+      </c>
+      <c r="B690" t="inlineStr">
+        <is>
+          <t>Qwen3.6</t>
+        </is>
+      </c>
+      <c r="C690" t="inlineStr">
+        <is>
+          <t>Qwen3.6-27B</t>
+        </is>
+      </c>
+      <c r="D690" t="n">
+        <v>27</v>
+      </c>
+      <c r="E690" t="inlineStr">
+        <is>
+          <t>Dense (multimodal)</t>
+        </is>
+      </c>
+      <c r="F690" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="G690" t="inlineStr">
+        <is>
+          <t>Thinking (default)</t>
+        </is>
+      </c>
+      <c r="H690" t="inlineStr">
+        <is>
+          <t>MathVision (no CI)</t>
+        </is>
+      </c>
+      <c r="I690" t="inlineStr">
+        <is>
+          <t>vision</t>
+        </is>
+      </c>
+      <c r="J690" t="n">
+        <v>85.09999999999999</v>
+      </c>
+      <c r="K690" t="inlineStr">
+        <is>
+          <t>huggingface.co/Qwen/Qwen3.8-27B card table, comparison column (Claude Code harness re-run; matches the Qwen3.6 card on all four overlapping benchmarks; extracted 2026-08)</t>
+        </is>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" t="inlineStr">
+        <is>
+          <t>Qwen</t>
+        </is>
+      </c>
+      <c r="B691" t="inlineStr">
+        <is>
+          <t>Qwen3.8</t>
+        </is>
+      </c>
+      <c r="C691" t="inlineStr">
+        <is>
+          <t>Qwen3.8-27B</t>
+        </is>
+      </c>
+      <c r="D691" t="n">
+        <v>27</v>
+      </c>
+      <c r="E691" t="inlineStr">
+        <is>
+          <t>Dense (multimodal)</t>
+        </is>
+      </c>
+      <c r="F691" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="G691" t="inlineStr">
+        <is>
+          <t>Thinking (default)</t>
+        </is>
+      </c>
+      <c r="H691" t="inlineStr">
+        <is>
+          <t>MathVision (with CI)</t>
+        </is>
+      </c>
+      <c r="I691" t="inlineStr">
+        <is>
+          <t>vision, CI</t>
+        </is>
+      </c>
+      <c r="J691" t="n">
+        <v>94.59999999999999</v>
+      </c>
+      <c r="K691" t="inlineStr">
+        <is>
+          <t>huggingface.co/Qwen/Qwen3.8-27B (live card, extracted 2026-08)</t>
+        </is>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" t="inlineStr">
+        <is>
+          <t>Qwen</t>
+        </is>
+      </c>
+      <c r="B692" t="inlineStr">
+        <is>
+          <t>Qwen3.6</t>
+        </is>
+      </c>
+      <c r="C692" t="inlineStr">
+        <is>
+          <t>Qwen3.6-27B</t>
+        </is>
+      </c>
+      <c r="D692" t="n">
+        <v>27</v>
+      </c>
+      <c r="E692" t="inlineStr">
+        <is>
+          <t>Dense (multimodal)</t>
+        </is>
+      </c>
+      <c r="F692" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="G692" t="inlineStr">
+        <is>
+          <t>Thinking (default)</t>
+        </is>
+      </c>
+      <c r="H692" t="inlineStr">
+        <is>
+          <t>MathVision (with CI)</t>
+        </is>
+      </c>
+      <c r="I692" t="inlineStr">
+        <is>
+          <t>vision, CI</t>
+        </is>
+      </c>
+      <c r="J692" t="n">
+        <v>90</v>
+      </c>
+      <c r="K692" t="inlineStr">
+        <is>
+          <t>huggingface.co/Qwen/Qwen3.8-27B card table, comparison column (Claude Code harness re-run; matches the Qwen3.6 card on all four overlapping benchmarks; extracted 2026-08)</t>
+        </is>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" t="inlineStr">
+        <is>
+          <t>Qwen</t>
+        </is>
+      </c>
+      <c r="B693" t="inlineStr">
+        <is>
+          <t>Qwen3.8</t>
+        </is>
+      </c>
+      <c r="C693" t="inlineStr">
+        <is>
+          <t>Qwen3.8-27B</t>
+        </is>
+      </c>
+      <c r="D693" t="n">
+        <v>27</v>
+      </c>
+      <c r="E693" t="inlineStr">
+        <is>
+          <t>Dense (multimodal)</t>
+        </is>
+      </c>
+      <c r="F693" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="G693" t="inlineStr">
+        <is>
+          <t>Thinking (default)</t>
+        </is>
+      </c>
+      <c r="H693" t="inlineStr">
+        <is>
+          <t>BabyVision (no CI)</t>
+        </is>
+      </c>
+      <c r="I693" t="inlineStr">
+        <is>
+          <t>vision</t>
+        </is>
+      </c>
+      <c r="J693" t="n">
+        <v>65.7</v>
+      </c>
+      <c r="K693" t="inlineStr">
+        <is>
+          <t>huggingface.co/Qwen/Qwen3.8-27B (live card, extracted 2026-08)</t>
+        </is>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" t="inlineStr">
+        <is>
+          <t>Qwen</t>
+        </is>
+      </c>
+      <c r="B694" t="inlineStr">
+        <is>
+          <t>Qwen3.6</t>
+        </is>
+      </c>
+      <c r="C694" t="inlineStr">
+        <is>
+          <t>Qwen3.6-27B</t>
+        </is>
+      </c>
+      <c r="D694" t="n">
+        <v>27</v>
+      </c>
+      <c r="E694" t="inlineStr">
+        <is>
+          <t>Dense (multimodal)</t>
+        </is>
+      </c>
+      <c r="F694" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="G694" t="inlineStr">
+        <is>
+          <t>Thinking (default)</t>
+        </is>
+      </c>
+      <c r="H694" t="inlineStr">
+        <is>
+          <t>BabyVision (no CI)</t>
+        </is>
+      </c>
+      <c r="I694" t="inlineStr">
+        <is>
+          <t>vision</t>
+        </is>
+      </c>
+      <c r="J694" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="K694" t="inlineStr">
+        <is>
+          <t>huggingface.co/Qwen/Qwen3.8-27B card table, comparison column (Claude Code harness re-run; matches the Qwen3.6 card on all four overlapping benchmarks; extracted 2026-08)</t>
+        </is>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" t="inlineStr">
+        <is>
+          <t>Qwen</t>
+        </is>
+      </c>
+      <c r="B695" t="inlineStr">
+        <is>
+          <t>Qwen3.8</t>
+        </is>
+      </c>
+      <c r="C695" t="inlineStr">
+        <is>
+          <t>Qwen3.8-27B</t>
+        </is>
+      </c>
+      <c r="D695" t="n">
+        <v>27</v>
+      </c>
+      <c r="E695" t="inlineStr">
+        <is>
+          <t>Dense (multimodal)</t>
+        </is>
+      </c>
+      <c r="F695" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="G695" t="inlineStr">
+        <is>
+          <t>Thinking (default)</t>
+        </is>
+      </c>
+      <c r="H695" t="inlineStr">
+        <is>
+          <t>BabyVision (with CI)</t>
+        </is>
+      </c>
+      <c r="I695" t="inlineStr">
+        <is>
+          <t>vision, CI</t>
+        </is>
+      </c>
+      <c r="J695" t="n">
+        <v>85.59999999999999</v>
+      </c>
+      <c r="K695" t="inlineStr">
+        <is>
+          <t>huggingface.co/Qwen/Qwen3.8-27B (live card, extracted 2026-08)</t>
+        </is>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" t="inlineStr">
+        <is>
+          <t>Qwen</t>
+        </is>
+      </c>
+      <c r="B696" t="inlineStr">
+        <is>
+          <t>Qwen3.8</t>
+        </is>
+      </c>
+      <c r="C696" t="inlineStr">
+        <is>
+          <t>Qwen3.8-27B</t>
+        </is>
+      </c>
+      <c r="D696" t="n">
+        <v>27</v>
+      </c>
+      <c r="E696" t="inlineStr">
+        <is>
+          <t>Dense (multimodal)</t>
+        </is>
+      </c>
+      <c r="F696" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="G696" t="inlineStr">
+        <is>
+          <t>Thinking (default)</t>
+        </is>
+      </c>
+      <c r="H696" t="inlineStr">
+        <is>
+          <t>CharXiv (no CI)</t>
+        </is>
+      </c>
+      <c r="I696" t="inlineStr">
+        <is>
+          <t>vision</t>
+        </is>
+      </c>
+      <c r="J696" t="n">
+        <v>83.7</v>
+      </c>
+      <c r="K696" t="inlineStr">
+        <is>
+          <t>huggingface.co/Qwen/Qwen3.8-27B (live card, extracted 2026-08)</t>
+        </is>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" t="inlineStr">
+        <is>
+          <t>Qwen</t>
+        </is>
+      </c>
+      <c r="B697" t="inlineStr">
+        <is>
+          <t>Qwen3.6</t>
+        </is>
+      </c>
+      <c r="C697" t="inlineStr">
+        <is>
+          <t>Qwen3.6-27B</t>
+        </is>
+      </c>
+      <c r="D697" t="n">
+        <v>27</v>
+      </c>
+      <c r="E697" t="inlineStr">
+        <is>
+          <t>Dense (multimodal)</t>
+        </is>
+      </c>
+      <c r="F697" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="G697" t="inlineStr">
+        <is>
+          <t>Thinking (default)</t>
+        </is>
+      </c>
+      <c r="H697" t="inlineStr">
+        <is>
+          <t>CharXiv (no CI)</t>
+        </is>
+      </c>
+      <c r="I697" t="inlineStr">
+        <is>
+          <t>vision</t>
+        </is>
+      </c>
+      <c r="J697" t="n">
+        <v>78.40000000000001</v>
+      </c>
+      <c r="K697" t="inlineStr">
+        <is>
+          <t>huggingface.co/Qwen/Qwen3.8-27B card table, comparison column (Claude Code harness re-run; matches the Qwen3.6 card on all four overlapping benchmarks; extracted 2026-08)</t>
+        </is>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" t="inlineStr">
+        <is>
+          <t>Qwen</t>
+        </is>
+      </c>
+      <c r="B698" t="inlineStr">
+        <is>
+          <t>Qwen3.8</t>
+        </is>
+      </c>
+      <c r="C698" t="inlineStr">
+        <is>
+          <t>Qwen3.8-27B</t>
+        </is>
+      </c>
+      <c r="D698" t="n">
+        <v>27</v>
+      </c>
+      <c r="E698" t="inlineStr">
+        <is>
+          <t>Dense (multimodal)</t>
+        </is>
+      </c>
+      <c r="F698" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="G698" t="inlineStr">
+        <is>
+          <t>Thinking (default)</t>
+        </is>
+      </c>
+      <c r="H698" t="inlineStr">
+        <is>
+          <t>CharXiv (with CI)</t>
+        </is>
+      </c>
+      <c r="I698" t="inlineStr">
+        <is>
+          <t>vision, CI</t>
+        </is>
+      </c>
+      <c r="J698" t="n">
+        <v>90.2</v>
+      </c>
+      <c r="K698" t="inlineStr">
+        <is>
+          <t>huggingface.co/Qwen/Qwen3.8-27B (live card, extracted 2026-08)</t>
+        </is>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" t="inlineStr">
+        <is>
+          <t>Qwen</t>
+        </is>
+      </c>
+      <c r="B699" t="inlineStr">
+        <is>
+          <t>Qwen3.8</t>
+        </is>
+      </c>
+      <c r="C699" t="inlineStr">
+        <is>
+          <t>Qwen3.8-27B</t>
+        </is>
+      </c>
+      <c r="D699" t="n">
+        <v>27</v>
+      </c>
+      <c r="E699" t="inlineStr">
+        <is>
+          <t>Dense (multimodal)</t>
+        </is>
+      </c>
+      <c r="F699" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="G699" t="inlineStr">
+        <is>
+          <t>Thinking (default)</t>
+        </is>
+      </c>
+      <c r="H699" t="inlineStr">
+        <is>
+          <t>OmniDocBench 1.5</t>
+        </is>
+      </c>
+      <c r="I699" t="inlineStr"/>
+      <c r="J699" t="n">
+        <v>91.09999999999999</v>
+      </c>
+      <c r="K699" t="inlineStr">
+        <is>
+          <t>huggingface.co/Qwen/Qwen3.8-27B (live card, extracted 2026-08)</t>
+        </is>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" t="inlineStr">
+        <is>
+          <t>Qwen</t>
+        </is>
+      </c>
+      <c r="B700" t="inlineStr">
+        <is>
+          <t>Qwen3.6</t>
+        </is>
+      </c>
+      <c r="C700" t="inlineStr">
+        <is>
+          <t>Qwen3.6-27B</t>
+        </is>
+      </c>
+      <c r="D700" t="n">
+        <v>27</v>
+      </c>
+      <c r="E700" t="inlineStr">
+        <is>
+          <t>Dense (multimodal)</t>
+        </is>
+      </c>
+      <c r="F700" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="G700" t="inlineStr">
+        <is>
+          <t>Thinking (default)</t>
+        </is>
+      </c>
+      <c r="H700" t="inlineStr">
+        <is>
+          <t>OmniDocBench 1.5</t>
+        </is>
+      </c>
+      <c r="I700" t="inlineStr"/>
+      <c r="J700" t="n">
+        <v>89.40000000000001</v>
+      </c>
+      <c r="K700" t="inlineStr">
+        <is>
+          <t>huggingface.co/Qwen/Qwen3.8-27B card table, comparison column (Claude Code harness re-run; matches the Qwen3.6 card on all four overlapping benchmarks; extracted 2026-08)</t>
+        </is>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" t="inlineStr">
+        <is>
+          <t>Qwen</t>
+        </is>
+      </c>
+      <c r="B701" t="inlineStr">
+        <is>
+          <t>Qwen3.8</t>
+        </is>
+      </c>
+      <c r="C701" t="inlineStr">
+        <is>
+          <t>Qwen3.8-27B</t>
+        </is>
+      </c>
+      <c r="D701" t="n">
+        <v>27</v>
+      </c>
+      <c r="E701" t="inlineStr">
+        <is>
+          <t>Dense (multimodal)</t>
+        </is>
+      </c>
+      <c r="F701" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="G701" t="inlineStr">
+        <is>
+          <t>Thinking (default)</t>
+        </is>
+      </c>
+      <c r="H701" t="inlineStr">
+        <is>
+          <t>RealWorldQA</t>
+        </is>
+      </c>
+      <c r="I701" t="inlineStr">
+        <is>
+          <t>vision</t>
+        </is>
+      </c>
+      <c r="J701" t="n">
+        <v>85.90000000000001</v>
+      </c>
+      <c r="K701" t="inlineStr">
+        <is>
+          <t>huggingface.co/Qwen/Qwen3.8-27B (live card, extracted 2026-08)</t>
+        </is>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" t="inlineStr">
+        <is>
+          <t>Qwen</t>
+        </is>
+      </c>
+      <c r="B702" t="inlineStr">
+        <is>
+          <t>Qwen3.6</t>
+        </is>
+      </c>
+      <c r="C702" t="inlineStr">
+        <is>
+          <t>Qwen3.6-27B</t>
+        </is>
+      </c>
+      <c r="D702" t="n">
+        <v>27</v>
+      </c>
+      <c r="E702" t="inlineStr">
+        <is>
+          <t>Dense (multimodal)</t>
+        </is>
+      </c>
+      <c r="F702" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="G702" t="inlineStr">
+        <is>
+          <t>Thinking (default)</t>
+        </is>
+      </c>
+      <c r="H702" t="inlineStr">
+        <is>
+          <t>RealWorldQA</t>
+        </is>
+      </c>
+      <c r="I702" t="inlineStr">
+        <is>
+          <t>vision</t>
+        </is>
+      </c>
+      <c r="J702" t="n">
+        <v>84.09999999999999</v>
+      </c>
+      <c r="K702" t="inlineStr">
+        <is>
+          <t>huggingface.co/Qwen/Qwen3.8-27B card table, comparison column (Claude Code harness re-run; matches the Qwen3.6 card on all four overlapping benchmarks; extracted 2026-08)</t>
+        </is>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" t="inlineStr">
+        <is>
+          <t>Qwen</t>
+        </is>
+      </c>
+      <c r="B703" t="inlineStr">
+        <is>
+          <t>Qwen3.8</t>
+        </is>
+      </c>
+      <c r="C703" t="inlineStr">
+        <is>
+          <t>Qwen3.8-27B</t>
+        </is>
+      </c>
+      <c r="D703" t="n">
+        <v>27</v>
+      </c>
+      <c r="E703" t="inlineStr">
+        <is>
+          <t>Dense (multimodal)</t>
+        </is>
+      </c>
+      <c r="F703" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="G703" t="inlineStr">
+        <is>
+          <t>Thinking (default)</t>
+        </is>
+      </c>
+      <c r="H703" t="inlineStr">
+        <is>
+          <t>ERQA</t>
+        </is>
+      </c>
+      <c r="I703" t="inlineStr">
+        <is>
+          <t>vision</t>
+        </is>
+      </c>
+      <c r="J703" t="n">
+        <v>65.5</v>
+      </c>
+      <c r="K703" t="inlineStr">
+        <is>
+          <t>huggingface.co/Qwen/Qwen3.8-27B (live card, extracted 2026-08)</t>
+        </is>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" t="inlineStr">
+        <is>
+          <t>Qwen</t>
+        </is>
+      </c>
+      <c r="B704" t="inlineStr">
+        <is>
+          <t>Qwen3.6</t>
+        </is>
+      </c>
+      <c r="C704" t="inlineStr">
+        <is>
+          <t>Qwen3.6-27B</t>
+        </is>
+      </c>
+      <c r="D704" t="n">
+        <v>27</v>
+      </c>
+      <c r="E704" t="inlineStr">
+        <is>
+          <t>Dense (multimodal)</t>
+        </is>
+      </c>
+      <c r="F704" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="G704" t="inlineStr">
+        <is>
+          <t>Thinking (default)</t>
+        </is>
+      </c>
+      <c r="H704" t="inlineStr">
+        <is>
+          <t>ERQA</t>
+        </is>
+      </c>
+      <c r="I704" t="inlineStr">
+        <is>
+          <t>vision</t>
+        </is>
+      </c>
+      <c r="J704" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="K704" t="inlineStr">
+        <is>
+          <t>huggingface.co/Qwen/Qwen3.8-27B card table, comparison column (Claude Code harness re-run; matches the Qwen3.6 card on all four overlapping benchmarks; extracted 2026-08)</t>
         </is>
       </c>
     </row>
